--- a/設計書/テスト仕様書_UI.xlsx
+++ b/設計書/テスト仕様書_UI.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2434,6 +2434,487 @@
       <c r="H53" s="2" t="n"/>
       <c r="I53" s="2" t="n"/>
     </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>ホーム画面</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>F12</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>代理変更ダイアログの外側タップでの終了</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>自分が管理者、ダイアログを開いている</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>ダイアログ背景の暗い部分をタップする</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>状態を変更せずにダイアログが閉じる</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="n"/>
+      <c r="I54" s="2" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>ホーム画面</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>F19</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>管理者によるメンバー削除</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>自分が管理者、対象メンバーの状態変更ダイアログを開いている</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>「このメンバーを削除する」→確認ダイアログで「削除する」</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>対象メンバーが一覧から消え、対象メンバーの端末はこのグループを見られなくなる</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="n"/>
+      <c r="I55" s="2" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>設定画面</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>F18</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>参加している他のグループの一覧表示</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>2つ以上の家族グループに参加している</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>設定画面を開く</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>参加中の各グループが一覧表示され、いま表示中のグループが分かる</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="n"/>
+      <c r="I56" s="2" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>設定画面</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>F18</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>別グループへの切り替え</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>2つ以上の家族グループに参加している</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>一覧の「切り替え」ボタンを押す</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>ホーム画面が押したグループの内容(メンバー一覧・自分の状態)に切り替わる</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="n"/>
+      <c r="I57" s="2" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>設定画面</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>F18</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>別の招待コードでの追加参加</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>既に1つ以上のグループに参加している</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>「別の招待コードで参加する」→招待コードと名前を入力し参加する</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既存の参加を維持したまま新しいグループにも参加し、そのグループに切り替わる</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="n"/>
+      <c r="I58" s="2" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>設定画面</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>F20</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>管理者によるグループ削除</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>自分が管理者</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>「グループを削除する」→取り消せない旨の確認ダイアログで「削除する」</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>グループと全メンバーが削除され、他に参加中のグループがあればそちらへ、無ければスタート画面に遷移する</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="n"/>
+      <c r="I59" s="2" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>設定画面</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>F20</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>管理者以外への削除ボタンの非表示</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>自分が管理者でない</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>設定画面を開く</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>「グループを削除する」ボタンが表示されない</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="n"/>
+      <c r="I60" s="2" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Web版(わが家)</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>F12</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>代理変更モーダルの外側タップでの終了</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>自分が管理者、モーダルを開いている</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>モーダル背景の暗い部分をタップする</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>状態を変更せずにモーダルが閉じる</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="n"/>
+      <c r="I61" s="2" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Web版(わが家)</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>F19</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>管理者によるメンバー削除</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>自分が管理者</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>対象メンバーをタップ→「このメンバーを削除する」→確認ダイアログでOK</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>対象メンバーが一覧から消える</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="n"/>
+      <c r="I62" s="2" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Web版(設定)</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>F18</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>参加している他のグループの一覧・切替</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>2つ以上の家族グループに参加している</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>「家族グループ」欄の「切り替え」を押す</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>表示中のグループが切り替わる</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="n"/>
+      <c r="I63" s="2" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Web版(設定)</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>F18</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>別の招待コードでの追加参加</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>既に1つ以上のグループに参加している</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>「別の招待コードで参加する」→招待コードと名前を入力し参加する</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>参加画面に「キャンセルして戻る」が表示され、参加すると新しいグループに切り替わる</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="n"/>
+      <c r="I64" s="2" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Web版(設定)</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>F20</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>管理者によるグループ削除</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>自分が管理者</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>「グループを削除する」→確認ダイアログでOK</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>グループと全メンバーが削除される</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="n"/>
+      <c r="I65" s="2" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Web版</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>F14</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>localStorage消失からの復元</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>以前に参加済みで、ブラウザのlocalStorageが何らかの理由で消えている</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>ページを開く(または再読み込みする)</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>cookieに複製されたバックアップから参加情報が復元され、招待コード入力画面に戻らずホーム画面が表示される</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="n"/>
+      <c r="I66" s="2" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/設計書/テスト仕様書_UI.xlsx
+++ b/設計書/テスト仕様書_UI.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:I69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2915,6 +2915,117 @@
       <c r="H66" s="2" t="n"/>
       <c r="I66" s="2" t="n"/>
     </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>設定画面</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>F18</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>参加中グループ一覧のDB同期</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>端末内の保存内容と実際の参加状況がずれている(端末再インストール等)</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>設定画面を開く</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>DBから取得した最新の参加状況で一覧が更新され、実際に参加しているグループが正しく表示される</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="n"/>
+      <c r="I67" s="2" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>設定画面</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>F18</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>一覧での招待コード表示</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>2つ以上の家族グループに参加している</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>「参加している他のグループ」欄を確認する</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>いま表示中でない各グループの行に招待コードが表示され、同名メンバーがいても区別できる</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="n"/>
+      <c r="I68" s="2" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Web版</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>F18</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>参加中グループ一覧のDB同期</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>端末内の保存内容と実際の参加状況がずれている</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>ページを開く、または「更新」ボタンを押す</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>DBから取得した最新の参加状況で一覧が更新される</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="n"/>
+      <c r="I69" s="2" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/設計書/テスト仕様書_UI.xlsx
+++ b/設計書/テスト仕様書_UI.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:I75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3026,6 +3026,228 @@
       <c r="H69" s="2" t="n"/>
       <c r="I69" s="2" t="n"/>
     </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>ホーム画面</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>F21</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>並び替えの既定順</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>まだ並び替えを行ったことがない</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>ホーム画面を開く</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>自分の行が一覧の先頭に表示される</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="n"/>
+      <c r="I70" s="2" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>ホーム画面</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>F21</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>ドラッグ＆ドロップでの並び替え</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>行左端のハンドルアイコンを押したままドラッグし、離す</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>その端末の中で一覧の並び順が変わり、次回起動後も同じ並びが維持される</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="n"/>
+      <c r="I71" s="2" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>ホーム画面</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>F21</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>新規参加者の並び順</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>並び替え済みの状態で、新しいメンバーがグループに参加する</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>ホーム画面を更新する</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>新しいメンバーは一覧の末尾に追加され、既存の並び順は崩れない</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="n"/>
+      <c r="I72" s="2" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Web版(設定)</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>F22</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>自宅の現在地登録</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>「現在地を自宅として登録する」を押し、位置情報の利用を許可する</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>在宅100m・施設内300mの初期値で自宅位置が登録され、「登録済みです」の表示に変わる</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="n"/>
+      <c r="I73" s="2" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Web版(わが家)</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>F22</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>画面を開いた瞬間の自動判定</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>自宅が登録済みで、現在地が在宅範囲の外にいる状態で外出中になっている</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>自宅の範囲内から改めてページを開く（または再読み込みする）</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>位置情報の許可後、自動的に「在宅」へ切り替わり、家族に通知される(通知設定ONの端末のみ)</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="n"/>
+      <c r="I74" s="2" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Web版(わが家)</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>F22</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>位置情報が使えない場合のフォールバック</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>自宅が登録済みだが、位置情報の利用を拒否する</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>ページを開く</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>エラー表示はされず、現在の状態のまま維持される（手動切替は引き続き使える）</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="n"/>
+      <c r="I75" s="2" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/設計書/テスト仕様書_UI.xlsx
+++ b/設計書/テスト仕様書_UI.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I75"/>
+  <dimension ref="A1:I76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3248,6 +3248,43 @@
       <c r="H75" s="2" t="n"/>
       <c r="I75" s="2" t="n"/>
     </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Web版(わが家)</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>F21</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>ドラッグ＆ドロップでの並び替え</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>行左端のハンドルアイコンを指で押したまま動かし、離す</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>その端末の中で一覧の並び順が変わり、再読み込み後も同じ並びが維持される</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="n"/>
+      <c r="I76" s="2" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/設計書/テスト仕様書_UI.xlsx
+++ b/設計書/テスト仕様書_UI.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I76"/>
+  <dimension ref="A1:I82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3285,6 +3285,228 @@
       <c r="H76" s="2" t="n"/>
       <c r="I76" s="2" t="n"/>
     </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>自宅の登録画面</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>施設内範囲ラベルの表示崩れ修正</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>「マンション内など「近くにいる」と判定する範囲」の行を確認する</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>長いラベルでも実際のメートル数（例：300m）が見切れずに表示される</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="n"/>
+      <c r="I77" s="2" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>設定画面</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>F23</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>プライバシーポリシーの表示</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>「このアプリについて」→「プライバシーポリシー」をタップする</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>プライバシーポリシー画面に遷移し、内容が表示される</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="n"/>
+      <c r="I78" s="2" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>設定画面</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>F23</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>バージョン番号の表示</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>「このアプリについて」欄を確認する</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>現在のアプリのバージョン番号（例：1.1.0）が表示される</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="n"/>
+      <c r="I79" s="2" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Web版(設定)</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>F23</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>プライバシーポリシーの表示</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>「このアプリについて」→「プライバシーポリシー」を開く</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>/privacy.html が開き、内容が表示される</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="n"/>
+      <c r="I80" s="2" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Web版(設定)</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>F23</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>バージョン番号の表示</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>「このアプリについて」欄を確認する</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>現在のバージョン番号（例：1.1.0）が表示される</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="n"/>
+      <c r="I81" s="2" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>招待コードで参加する画面</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>再インストール後の復帰</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>以前このグループに参加したことがある名前で、別のdevice_id(再インストール後など)から参加する</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>招待コードと以前と同じ名前を入力して参加する</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>新規メンバーとして重複登録されず、以前の状態（ステータス・管理者バッジなど）を引き継いだまま一覧に表示される</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="n"/>
+      <c r="I82" s="2" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/設計書/テスト仕様書_UI.xlsx
+++ b/設計書/テスト仕様書_UI.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I82"/>
+  <dimension ref="A1:I83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3507,6 +3507,43 @@
       <c r="H82" s="2" t="n"/>
       <c r="I82" s="2" t="n"/>
     </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>招待コードで参加する画面</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>F2/F3</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>復帰時・自宅登録済みの場合の画面省略</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>以前このグループで自宅位置を登録済みの名前で、別の端末(再インストール後など)から参加する</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>招待コードと以前と同じ名前を入力して参加する</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>自宅の登録画面を経由せず、直接ホーム画面が表示される。バックグラウンドの自動判定も再登録される</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="n"/>
+      <c r="I83" s="2" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/設計書/テスト仕様書_UI.xlsx
+++ b/設計書/テスト仕様書_UI.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I83"/>
+  <dimension ref="A1:I85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3544,6 +3544,80 @@
       <c r="H83" s="2" t="n"/>
       <c r="I83" s="2" t="n"/>
     </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>ホーム画面</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>F12</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>管理者が代理変更した直後は、時刻を表示せず通知もされない</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>管理者が家族の名前を長押し(Web版はタップ)して、ステータス変更メニューを開いている</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>メニューから別のステータス(例:在宅)を選んで変更する</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>対象メンバーの行は、変更後のステータスのラベルのみ表示され、時刻(「18:32に帰宅」等)は表示されない。対象メンバーの端末には通知が届かない</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="n"/>
+      <c r="I84" s="2" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>ホーム画面</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>F12</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>管理者による代理変更の後、本人が自分で変更すると通常表示に戻る</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>直前の操作で管理者がそのメンバーの状態を代理変更している</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>対象メンバー本人の端末で、3択スイッチから状態を切り替える</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>一覧を更新すると、その行には通常どおり最終更新時刻が表示され、他メンバーに通知も届く</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="n"/>
+      <c r="I85" s="2" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
